--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -21879,7 +21879,7 @@
         <v>117451692</v>
       </c>
       <c r="B198" t="n">
-        <v>96423</v>
+        <v>96425</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -21991,7 +21991,7 @@
         <v>119738980</v>
       </c>
       <c r="B199" t="n">
-        <v>94323</v>
+        <v>94346</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>119920840</v>
       </c>
       <c r="B200" t="n">
-        <v>56204</v>
+        <v>56214</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22103,11 +22103,11 @@
         <v>119920840</v>
       </c>
       <c r="B200" t="n">
-        <v>56214</v>
+        <v>56251</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22103,7 +22103,7 @@
         <v>119920840</v>
       </c>
       <c r="B200" t="n">
-        <v>56251</v>
+        <v>56259</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -21972,7 +21972,7 @@
         <v>119920840</v>
       </c>
       <c r="B199" t="n">
-        <v>56259</v>
+        <v>56263</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -21972,7 +21972,7 @@
         <v>119920840</v>
       </c>
       <c r="B199" t="n">
-        <v>56263</v>
+        <v>56264</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -21972,7 +21972,7 @@
         <v>119920840</v>
       </c>
       <c r="B199" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY199"/>
+  <dimension ref="A1:AY204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22092,6 +22092,536 @@
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>122753502</v>
+      </c>
+      <c r="B200" t="n">
+        <v>86479</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Smedsrönningen SV, Gstr</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>574530</v>
+      </c>
+      <c r="R200" t="n">
+        <v>6703442</v>
+      </c>
+      <c r="S200" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AD200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG200" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT200" t="inlineStr"/>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>122753505</v>
+      </c>
+      <c r="B201" t="n">
+        <v>100520</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Fännsmyran S, Gstr</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>574278</v>
+      </c>
+      <c r="R201" t="n">
+        <v>6703471</v>
+      </c>
+      <c r="S201" t="n">
+        <v>10</v>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG201" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT201" t="inlineStr"/>
+      <c r="AW201" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX201" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>122753507</v>
+      </c>
+      <c r="B202" t="n">
+        <v>86420</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr"/>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Rismyran SV, Gstr</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>574322</v>
+      </c>
+      <c r="R202" t="n">
+        <v>6703415</v>
+      </c>
+      <c r="S202" t="n">
+        <v>10</v>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG202" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT202" t="inlineStr"/>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>122753508</v>
+      </c>
+      <c r="B203" t="n">
+        <v>90485</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Fännsmyran SV, Gstr</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>574334</v>
+      </c>
+      <c r="R203" t="n">
+        <v>6703351</v>
+      </c>
+      <c r="S203" t="n">
+        <v>10</v>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG203" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT203" t="inlineStr"/>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>122753503</v>
+      </c>
+      <c r="B204" t="n">
+        <v>90475</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Slätahällsm. V, Gstr</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>574232</v>
+      </c>
+      <c r="R204" t="n">
+        <v>6703559</v>
+      </c>
+      <c r="S204" t="n">
+        <v>10</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22097,7 +22097,7 @@
         <v>122753502</v>
       </c>
       <c r="B200" t="n">
-        <v>86479</v>
+        <v>86481</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22200,10 +22200,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753505</v>
+        <v>122753508</v>
       </c>
       <c r="B201" t="n">
-        <v>100520</v>
+        <v>90487</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22212,38 +22212,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574278</v>
+        <v>574334</v>
       </c>
       <c r="R201" t="n">
-        <v>6703471</v>
+        <v>6703351</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22309,7 +22309,7 @@
         <v>122753507</v>
       </c>
       <c r="B202" t="n">
-        <v>86420</v>
+        <v>86422</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753508</v>
+        <v>122753505</v>
       </c>
       <c r="B203" t="n">
-        <v>90485</v>
+        <v>100522</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574334</v>
+        <v>574278</v>
       </c>
       <c r="R203" t="n">
-        <v>6703351</v>
+        <v>6703471</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22521,7 +22521,7 @@
         <v>122753503</v>
       </c>
       <c r="B204" t="n">
-        <v>90475</v>
+        <v>90477</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22097,7 +22097,7 @@
         <v>122753502</v>
       </c>
       <c r="B200" t="n">
-        <v>86481</v>
+        <v>86485</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22200,10 +22200,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753508</v>
+        <v>122753507</v>
       </c>
       <c r="B201" t="n">
-        <v>90487</v>
+        <v>86426</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22212,38 +22212,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5754</v>
+        <v>3674</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574334</v>
+        <v>574322</v>
       </c>
       <c r="R201" t="n">
-        <v>6703351</v>
+        <v>6703415</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753507</v>
+        <v>122753508</v>
       </c>
       <c r="B202" t="n">
-        <v>86422</v>
+        <v>90491</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3674</v>
+        <v>5754</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574322</v>
+        <v>574334</v>
       </c>
       <c r="R202" t="n">
-        <v>6703415</v>
+        <v>6703351</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753505</v>
+        <v>122753503</v>
       </c>
       <c r="B203" t="n">
-        <v>100522</v>
+        <v>90481</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>222771</v>
+        <v>5747</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574278</v>
+        <v>574232</v>
       </c>
       <c r="R203" t="n">
-        <v>6703471</v>
+        <v>6703559</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753503</v>
+        <v>122753505</v>
       </c>
       <c r="B204" t="n">
-        <v>90477</v>
+        <v>100530</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22530,38 +22530,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5747</v>
+        <v>222771</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574232</v>
+        <v>574278</v>
       </c>
       <c r="R204" t="n">
-        <v>6703559</v>
+        <v>6703471</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22094,10 +22094,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122753502</v>
+        <v>122753505</v>
       </c>
       <c r="B200" t="n">
-        <v>86485</v>
+        <v>100530</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22106,38 +22106,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3739</v>
+        <v>222771</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Smedsrönningen SV, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>574530</v>
+        <v>574278</v>
       </c>
       <c r="R200" t="n">
-        <v>6703442</v>
+        <v>6703471</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22164,12 +22164,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753503</v>
+        <v>122753502</v>
       </c>
       <c r="B203" t="n">
-        <v>90481</v>
+        <v>86485</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5747</v>
+        <v>3739</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Smedsrönningen SV, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574232</v>
+        <v>574530</v>
       </c>
       <c r="R203" t="n">
-        <v>6703559</v>
+        <v>6703442</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22482,12 +22482,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753505</v>
+        <v>122753503</v>
       </c>
       <c r="B204" t="n">
-        <v>100530</v>
+        <v>90481</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22530,38 +22530,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>222771</v>
+        <v>5747</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574278</v>
+        <v>574232</v>
       </c>
       <c r="R204" t="n">
-        <v>6703471</v>
+        <v>6703559</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22094,10 +22094,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122753505</v>
+        <v>122753502</v>
       </c>
       <c r="B200" t="n">
-        <v>100530</v>
+        <v>86485</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22106,38 +22106,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222771</v>
+        <v>3739</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Smedsrönningen SV, Gstr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>574278</v>
+        <v>574530</v>
       </c>
       <c r="R200" t="n">
-        <v>6703471</v>
+        <v>6703442</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22164,12 +22164,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22200,10 +22200,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753507</v>
+        <v>122753508</v>
       </c>
       <c r="B201" t="n">
-        <v>86426</v>
+        <v>90491</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22212,38 +22212,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3674</v>
+        <v>5754</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574322</v>
+        <v>574334</v>
       </c>
       <c r="R201" t="n">
-        <v>6703415</v>
+        <v>6703351</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753508</v>
+        <v>122753505</v>
       </c>
       <c r="B202" t="n">
-        <v>90491</v>
+        <v>100532</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574334</v>
+        <v>574278</v>
       </c>
       <c r="R202" t="n">
-        <v>6703351</v>
+        <v>6703471</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753502</v>
+        <v>122753507</v>
       </c>
       <c r="B203" t="n">
-        <v>86485</v>
+        <v>86426</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3739</v>
+        <v>3674</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Smedsrönningen SV, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574530</v>
+        <v>574322</v>
       </c>
       <c r="R203" t="n">
-        <v>6703442</v>
+        <v>6703415</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22482,12 +22482,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD203" t="b">

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22094,10 +22094,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122753502</v>
+        <v>122753505</v>
       </c>
       <c r="B200" t="n">
-        <v>86485</v>
+        <v>100532</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22106,38 +22106,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>3739</v>
+        <v>222771</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Smedsrönningen SV, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>574530</v>
+        <v>574278</v>
       </c>
       <c r="R200" t="n">
-        <v>6703442</v>
+        <v>6703471</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22164,12 +22164,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22200,10 +22200,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753508</v>
+        <v>122753502</v>
       </c>
       <c r="B201" t="n">
-        <v>90491</v>
+        <v>86485</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22216,34 +22216,34 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>5754</v>
+        <v>3739</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Smedsrönningen SV, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574334</v>
+        <v>574530</v>
       </c>
       <c r="R201" t="n">
-        <v>6703351</v>
+        <v>6703442</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22270,12 +22270,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753505</v>
+        <v>122753508</v>
       </c>
       <c r="B202" t="n">
-        <v>100532</v>
+        <v>90491</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574278</v>
+        <v>574334</v>
       </c>
       <c r="R202" t="n">
-        <v>6703471</v>
+        <v>6703351</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753507</v>
+        <v>122753503</v>
       </c>
       <c r="B203" t="n">
-        <v>86426</v>
+        <v>90481</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574322</v>
+        <v>574232</v>
       </c>
       <c r="R203" t="n">
-        <v>6703415</v>
+        <v>6703559</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753503</v>
+        <v>122753507</v>
       </c>
       <c r="B204" t="n">
-        <v>90481</v>
+        <v>86426</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22530,38 +22530,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574232</v>
+        <v>574322</v>
       </c>
       <c r="R204" t="n">
-        <v>6703559</v>
+        <v>6703415</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753508</v>
+        <v>122753507</v>
       </c>
       <c r="B202" t="n">
-        <v>90491</v>
+        <v>86426</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5754</v>
+        <v>3674</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574334</v>
+        <v>574322</v>
       </c>
       <c r="R202" t="n">
-        <v>6703351</v>
+        <v>6703415</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753503</v>
+        <v>122753508</v>
       </c>
       <c r="B203" t="n">
-        <v>90481</v>
+        <v>90491</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5747</v>
+        <v>5754</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574232</v>
+        <v>574334</v>
       </c>
       <c r="R203" t="n">
-        <v>6703559</v>
+        <v>6703351</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753507</v>
+        <v>122753503</v>
       </c>
       <c r="B204" t="n">
-        <v>86426</v>
+        <v>90481</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22530,38 +22530,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574322</v>
+        <v>574232</v>
       </c>
       <c r="R204" t="n">
-        <v>6703415</v>
+        <v>6703559</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753507</v>
+        <v>122753508</v>
       </c>
       <c r="B202" t="n">
-        <v>86426</v>
+        <v>90491</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3674</v>
+        <v>5754</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574322</v>
+        <v>574334</v>
       </c>
       <c r="R202" t="n">
-        <v>6703415</v>
+        <v>6703351</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753508</v>
+        <v>122753503</v>
       </c>
       <c r="B203" t="n">
-        <v>90491</v>
+        <v>90481</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5754</v>
+        <v>5747</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574334</v>
+        <v>574232</v>
       </c>
       <c r="R203" t="n">
-        <v>6703351</v>
+        <v>6703559</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753503</v>
+        <v>122753507</v>
       </c>
       <c r="B204" t="n">
-        <v>90481</v>
+        <v>86426</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22530,38 +22530,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574232</v>
+        <v>574322</v>
       </c>
       <c r="R204" t="n">
-        <v>6703559</v>
+        <v>6703415</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22094,10 +22094,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122753505</v>
+        <v>122753503</v>
       </c>
       <c r="B200" t="n">
-        <v>100532</v>
+        <v>90489</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22106,38 +22106,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222771</v>
+        <v>5747</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>574278</v>
+        <v>574232</v>
       </c>
       <c r="R200" t="n">
-        <v>6703471</v>
+        <v>6703559</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753508</v>
+        <v>122753507</v>
       </c>
       <c r="B202" t="n">
-        <v>90491</v>
+        <v>86426</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5754</v>
+        <v>3674</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574334</v>
+        <v>574322</v>
       </c>
       <c r="R202" t="n">
-        <v>6703351</v>
+        <v>6703415</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753503</v>
+        <v>122753508</v>
       </c>
       <c r="B203" t="n">
-        <v>90481</v>
+        <v>90499</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5747</v>
+        <v>5754</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574232</v>
+        <v>574334</v>
       </c>
       <c r="R203" t="n">
-        <v>6703559</v>
+        <v>6703351</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753507</v>
+        <v>122753505</v>
       </c>
       <c r="B204" t="n">
-        <v>86426</v>
+        <v>100540</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22534,34 +22534,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3674</v>
+        <v>222771</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574322</v>
+        <v>574278</v>
       </c>
       <c r="R204" t="n">
-        <v>6703415</v>
+        <v>6703471</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22094,10 +22094,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122753503</v>
+        <v>122753508</v>
       </c>
       <c r="B200" t="n">
-        <v>90489</v>
+        <v>90499</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22106,38 +22106,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5747</v>
+        <v>5754</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>574232</v>
+        <v>574334</v>
       </c>
       <c r="R200" t="n">
-        <v>6703559</v>
+        <v>6703351</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22200,10 +22200,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753502</v>
+        <v>122753507</v>
       </c>
       <c r="B201" t="n">
-        <v>86485</v>
+        <v>86426</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22212,38 +22212,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3739</v>
+        <v>3674</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Smedsrönningen SV, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574530</v>
+        <v>574322</v>
       </c>
       <c r="R201" t="n">
-        <v>6703442</v>
+        <v>6703415</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22270,12 +22270,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753507</v>
+        <v>122753503</v>
       </c>
       <c r="B202" t="n">
-        <v>86426</v>
+        <v>90489</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574322</v>
+        <v>574232</v>
       </c>
       <c r="R202" t="n">
-        <v>6703415</v>
+        <v>6703559</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753508</v>
+        <v>122753502</v>
       </c>
       <c r="B203" t="n">
-        <v>90499</v>
+        <v>86485</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22428,34 +22428,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5754</v>
+        <v>3739</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Smedsrönningen SV, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574334</v>
+        <v>574530</v>
       </c>
       <c r="R203" t="n">
-        <v>6703351</v>
+        <v>6703442</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22482,12 +22482,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD203" t="b">

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22200,10 +22200,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753507</v>
+        <v>122753502</v>
       </c>
       <c r="B201" t="n">
-        <v>86426</v>
+        <v>86485</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22212,38 +22212,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3674</v>
+        <v>3739</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Smedsrönningen SV, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574322</v>
+        <v>574530</v>
       </c>
       <c r="R201" t="n">
-        <v>6703415</v>
+        <v>6703442</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22270,12 +22270,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753503</v>
+        <v>122753507</v>
       </c>
       <c r="B202" t="n">
-        <v>90489</v>
+        <v>86426</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574232</v>
+        <v>574322</v>
       </c>
       <c r="R202" t="n">
-        <v>6703559</v>
+        <v>6703415</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753502</v>
+        <v>122753505</v>
       </c>
       <c r="B203" t="n">
-        <v>86485</v>
+        <v>100540</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3739</v>
+        <v>222771</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Smedsrönningen SV, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574530</v>
+        <v>574278</v>
       </c>
       <c r="R203" t="n">
-        <v>6703442</v>
+        <v>6703471</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22482,12 +22482,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753505</v>
+        <v>122753503</v>
       </c>
       <c r="B204" t="n">
-        <v>100540</v>
+        <v>90489</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22530,38 +22530,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>222771</v>
+        <v>5747</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574278</v>
+        <v>574232</v>
       </c>
       <c r="R204" t="n">
-        <v>6703471</v>
+        <v>6703559</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22200,10 +22200,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753502</v>
+        <v>122753505</v>
       </c>
       <c r="B201" t="n">
-        <v>86485</v>
+        <v>100540</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22212,38 +22212,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3739</v>
+        <v>222771</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Smedsrönningen SV, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574530</v>
+        <v>574278</v>
       </c>
       <c r="R201" t="n">
-        <v>6703442</v>
+        <v>6703471</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22270,12 +22270,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753505</v>
+        <v>122753502</v>
       </c>
       <c r="B203" t="n">
-        <v>100540</v>
+        <v>86485</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>222771</v>
+        <v>3739</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Smedsrönningen SV, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574278</v>
+        <v>574530</v>
       </c>
       <c r="R203" t="n">
-        <v>6703471</v>
+        <v>6703442</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22482,12 +22482,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD203" t="b">

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22097,7 +22097,7 @@
         <v>122753508</v>
       </c>
       <c r="B200" t="n">
-        <v>90499</v>
+        <v>90502</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>122753505</v>
       </c>
       <c r="B201" t="n">
-        <v>100540</v>
+        <v>100543</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753507</v>
+        <v>122753503</v>
       </c>
       <c r="B202" t="n">
-        <v>86426</v>
+        <v>90492</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574322</v>
+        <v>574232</v>
       </c>
       <c r="R202" t="n">
-        <v>6703415</v>
+        <v>6703559</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22415,7 +22415,7 @@
         <v>122753502</v>
       </c>
       <c r="B203" t="n">
-        <v>86485</v>
+        <v>86488</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753503</v>
+        <v>122753507</v>
       </c>
       <c r="B204" t="n">
-        <v>90489</v>
+        <v>86429</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22530,38 +22530,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574232</v>
+        <v>574322</v>
       </c>
       <c r="R204" t="n">
-        <v>6703559</v>
+        <v>6703415</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -22094,10 +22094,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122753508</v>
+        <v>122753505</v>
       </c>
       <c r="B200" t="n">
-        <v>90502</v>
+        <v>100545</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22106,38 +22106,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Fännsmyran SV, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>574334</v>
+        <v>574278</v>
       </c>
       <c r="R200" t="n">
-        <v>6703351</v>
+        <v>6703471</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22200,10 +22200,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753505</v>
+        <v>122753502</v>
       </c>
       <c r="B201" t="n">
-        <v>100543</v>
+        <v>86490</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22212,38 +22212,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>222771</v>
+        <v>3739</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Smedsrönningen SV, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574278</v>
+        <v>574530</v>
       </c>
       <c r="R201" t="n">
-        <v>6703471</v>
+        <v>6703442</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22270,12 +22270,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22306,10 +22306,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753503</v>
+        <v>122753507</v>
       </c>
       <c r="B202" t="n">
-        <v>90492</v>
+        <v>86431</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22318,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574232</v>
+        <v>574322</v>
       </c>
       <c r="R202" t="n">
-        <v>6703559</v>
+        <v>6703415</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22412,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753502</v>
+        <v>122753503</v>
       </c>
       <c r="B203" t="n">
-        <v>86488</v>
+        <v>90494</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22424,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>3739</v>
+        <v>5747</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Smedsrönningen SV, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574530</v>
+        <v>574232</v>
       </c>
       <c r="R203" t="n">
-        <v>6703442</v>
+        <v>6703559</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22482,12 +22482,12 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22518,10 +22518,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>122753507</v>
+        <v>122753508</v>
       </c>
       <c r="B204" t="n">
-        <v>86429</v>
+        <v>90504</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -22530,38 +22530,38 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3674</v>
+        <v>5754</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>574322</v>
+        <v>574334</v>
       </c>
       <c r="R204" t="n">
-        <v>6703415</v>
+        <v>6703351</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>

--- a/artfynd/A 14918-2023 artfynd.xlsx
+++ b/artfynd/A 14918-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY204"/>
+  <dimension ref="A1:AY203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17436,10 +17436,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>112204527</v>
+        <v>112204534</v>
       </c>
       <c r="B157" t="n">
-        <v>93271</v>
+        <v>85263</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -17452,21 +17452,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2813</v>
+        <v>3762</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17476,10 +17476,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>574434</v>
+        <v>574275</v>
       </c>
       <c r="R157" t="n">
-        <v>6703389</v>
+        <v>6703472</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -17538,10 +17538,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>112204534</v>
+        <v>112204546</v>
       </c>
       <c r="B158" t="n">
-        <v>85263</v>
+        <v>90874</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -17554,21 +17554,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17578,10 +17578,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>574275</v>
+        <v>574312</v>
       </c>
       <c r="R158" t="n">
-        <v>6703472</v>
+        <v>6703559</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -17640,10 +17640,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>112204546</v>
+        <v>112204519</v>
       </c>
       <c r="B159" t="n">
-        <v>90874</v>
+        <v>90519</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -17656,21 +17656,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17680,10 +17680,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>574312</v>
+        <v>574416</v>
       </c>
       <c r="R159" t="n">
-        <v>6703559</v>
+        <v>6703348</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -17742,10 +17742,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>112204519</v>
+        <v>112204496</v>
       </c>
       <c r="B160" t="n">
-        <v>90519</v>
+        <v>99924</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17758,21 +17758,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17782,10 +17782,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>574416</v>
+        <v>574374</v>
       </c>
       <c r="R160" t="n">
-        <v>6703348</v>
+        <v>6703549</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -17844,10 +17844,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>112204496</v>
+        <v>112204522</v>
       </c>
       <c r="B161" t="n">
-        <v>99924</v>
+        <v>90896</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17856,25 +17856,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221235</v>
+        <v>5448</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17884,10 +17884,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>574374</v>
+        <v>574380</v>
       </c>
       <c r="R161" t="n">
-        <v>6703549</v>
+        <v>6703524</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -17946,10 +17946,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>112204522</v>
+        <v>112204524</v>
       </c>
       <c r="B162" t="n">
-        <v>90896</v>
+        <v>98939</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17958,25 +17958,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5448</v>
+        <v>222771</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17986,10 +17986,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>574380</v>
+        <v>574284</v>
       </c>
       <c r="R162" t="n">
-        <v>6703524</v>
+        <v>6703462</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -18048,10 +18048,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>112204524</v>
+        <v>112204512</v>
       </c>
       <c r="B163" t="n">
-        <v>98939</v>
+        <v>90519</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -18064,21 +18064,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18088,10 +18088,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>574284</v>
+        <v>574381</v>
       </c>
       <c r="R163" t="n">
-        <v>6703462</v>
+        <v>6703524</v>
       </c>
       <c r="S163" t="n">
         <v>15</v>
@@ -18150,7 +18150,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>112204512</v>
+        <v>112204520</v>
       </c>
       <c r="B164" t="n">
         <v>90519</v>
@@ -18190,10 +18190,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>574381</v>
+        <v>574432</v>
       </c>
       <c r="R164" t="n">
-        <v>6703524</v>
+        <v>6703353</v>
       </c>
       <c r="S164" t="n">
         <v>15</v>
@@ -18252,10 +18252,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>112204520</v>
+        <v>112204509</v>
       </c>
       <c r="B165" t="n">
-        <v>90519</v>
+        <v>4721</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -18268,34 +18268,43 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4769</v>
+        <v>100299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Kratte Masugn, Gstr</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>574432</v>
+        <v>574304</v>
       </c>
       <c r="R165" t="n">
-        <v>6703353</v>
+        <v>6703522</v>
       </c>
       <c r="S165" t="n">
         <v>15</v>
@@ -18336,6 +18345,7 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
@@ -18354,10 +18364,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>112204509</v>
+        <v>112204528</v>
       </c>
       <c r="B166" t="n">
-        <v>4721</v>
+        <v>78686</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -18370,43 +18380,34 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100299</v>
+        <v>6456</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Kratte Masugn, Gstr</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>574304</v>
+        <v>574534</v>
       </c>
       <c r="R166" t="n">
-        <v>6703522</v>
+        <v>6703436</v>
       </c>
       <c r="S166" t="n">
         <v>15</v>
@@ -18447,7 +18448,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -18466,10 +18466,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>112204528</v>
+        <v>112204507</v>
       </c>
       <c r="B167" t="n">
-        <v>78686</v>
+        <v>102244</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -18482,21 +18482,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6456</v>
+        <v>222412</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18506,10 +18506,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>574534</v>
+        <v>574348</v>
       </c>
       <c r="R167" t="n">
-        <v>6703436</v>
+        <v>6703560</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -18568,10 +18568,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>112204507</v>
+        <v>112204558</v>
       </c>
       <c r="B168" t="n">
-        <v>102244</v>
+        <v>85427</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -18584,21 +18584,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>222412</v>
+        <v>3674</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18608,10 +18608,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>574348</v>
+        <v>574268</v>
       </c>
       <c r="R168" t="n">
-        <v>6703560</v>
+        <v>6703487</v>
       </c>
       <c r="S168" t="n">
         <v>15</v>
@@ -18670,10 +18670,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>112204558</v>
+        <v>112204500</v>
       </c>
       <c r="B169" t="n">
-        <v>85427</v>
+        <v>94340</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -18682,25 +18682,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3674</v>
+        <v>53</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18710,10 +18710,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>574268</v>
+        <v>574270</v>
       </c>
       <c r="R169" t="n">
-        <v>6703487</v>
+        <v>6703543</v>
       </c>
       <c r="S169" t="n">
         <v>15</v>
@@ -18772,10 +18772,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>112204500</v>
+        <v>112214964</v>
       </c>
       <c r="B170" t="n">
-        <v>94340</v>
+        <v>85487</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18788,37 +18788,48 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>53</v>
+        <v>3739</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Kratte Masugn, Gstr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>574270</v>
+        <v>574526</v>
       </c>
       <c r="R170" t="n">
-        <v>6703543</v>
+        <v>6703440</v>
       </c>
       <c r="S170" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18842,12 +18853,17 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-19</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Växte tillsammans med gran och några aspar. Rikligt med dofttaggsvamp intill.</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18856,28 +18872,29 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>112214964</v>
+        <v>112215002</v>
       </c>
       <c r="B171" t="n">
-        <v>85487</v>
+        <v>88179</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18886,30 +18903,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3739</v>
+        <v>1593</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -18925,13 +18942,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>574526</v>
+        <v>574226</v>
       </c>
       <c r="R171" t="n">
-        <v>6703440</v>
+        <v>6703548</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18965,7 +18982,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Växte tillsammans med gran och några aspar. Rikligt med dofttaggsvamp intill.</t>
+          <t>Väldigt annorlunda lokal och växtplats för en lakritsmusseron. Mestadels gran men det växte tallar i närheten också. Kalkbarrskog för övrigt och denna växte precis intill en läderdoftande fingersvamp. Fortfarande under mossan. Fruktkroppen hade den tydliga doften lakritsmusseron brukar ha.</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -18993,10 +19010,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>112215002</v>
+        <v>112215073</v>
       </c>
       <c r="B172" t="n">
-        <v>88179</v>
+        <v>85464</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -19005,30 +19022,30 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1593</v>
+        <v>6003295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -19044,13 +19061,13 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>574226</v>
+        <v>574312</v>
       </c>
       <c r="R172" t="n">
-        <v>6703548</v>
+        <v>6703375</v>
       </c>
       <c r="S172" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19084,7 +19101,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Väldigt annorlunda lokal och växtplats för en lakritsmusseron. Mestadels gran men det växte tallar i närheten också. Kalkbarrskog för övrigt och denna växte precis intill en läderdoftande fingersvamp. Fortfarande under mossan. Fruktkroppen hade den tydliga doften lakritsmusseron brukar ha.</t>
+          <t>Växte inom några meter ifrån Koppartaggsvamp.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19112,10 +19129,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>112215073</v>
+        <v>110388478</v>
       </c>
       <c r="B173" t="n">
-        <v>85464</v>
+        <v>97082</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -19124,52 +19141,42 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6003295</v>
+        <v>219790</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Kratte Masugn, Gstr</t>
+          <t>Gropbackagruvorna (Gropbackagruvorna), Gstr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>574312</v>
+        <v>574313</v>
       </c>
       <c r="R173" t="n">
-        <v>6703375</v>
+        <v>6703531</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19193,17 +19200,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Växte inom några meter ifrån Koppartaggsvamp.</t>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19212,29 +19224,28 @@
       <c r="AE173" t="b">
         <v>0</v>
       </c>
-      <c r="AF173" t="inlineStr"/>
       <c r="AG173" t="b">
         <v>0</v>
       </c>
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>110388478</v>
+        <v>113680436</v>
       </c>
       <c r="B174" t="n">
-        <v>97082</v>
+        <v>91648</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -19243,42 +19254,41 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>219790</v>
+        <v>5448</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Gropbackagruvorna (Gropbackagruvorna), Gstr</t>
+          <t>Gropbacka, Gstr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>574313</v>
+        <v>574384</v>
       </c>
       <c r="R174" t="n">
-        <v>6703531</v>
+        <v>6703522</v>
       </c>
       <c r="S174" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -19302,22 +19312,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>17:43</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>17:43</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19330,24 +19330,33 @@
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>fanny westling</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr"/>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>113680436</v>
+        <v>113680435</v>
       </c>
       <c r="B175" t="n">
-        <v>91648</v>
+        <v>90105</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -19356,38 +19365,38 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5448</v>
+        <v>3215</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Gropbacka, Gstr</t>
+          <t>Kalkberget, Gstr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>574384</v>
+        <v>574480</v>
       </c>
       <c r="R175" t="n">
-        <v>6703522</v>
+        <v>6703483</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19455,10 +19464,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>113680435</v>
+        <v>113680441</v>
       </c>
       <c r="B176" t="n">
-        <v>90105</v>
+        <v>91617</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -19471,34 +19480,34 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>3215</v>
+        <v>4366</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Kalkberget, Gstr</t>
+          <t>Gropbacka, Gstr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>574480</v>
+        <v>574207</v>
       </c>
       <c r="R176" t="n">
-        <v>6703483</v>
+        <v>6703511</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19566,10 +19575,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>113680441</v>
+        <v>113680440</v>
       </c>
       <c r="B177" t="n">
-        <v>91617</v>
+        <v>91623</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -19578,38 +19587,38 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4366</v>
+        <v>4368</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gropbacka, Gstr</t>
+          <t>vreten, Gstr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>574207</v>
+        <v>574252</v>
       </c>
       <c r="R177" t="n">
-        <v>6703511</v>
+        <v>6703540</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19677,10 +19686,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>113680440</v>
+        <v>113682614</v>
       </c>
       <c r="B178" t="n">
-        <v>91623</v>
+        <v>103146</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -19689,25 +19698,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4368</v>
+        <v>222412</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19717,10 +19726,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>574252</v>
+        <v>574350</v>
       </c>
       <c r="R178" t="n">
-        <v>6703540</v>
+        <v>6703556</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19764,12 +19773,12 @@
       <c r="AG178" t="b">
         <v>0</v>
       </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AT178" t="inlineStr"/>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW178" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -19788,10 +19797,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>113682614</v>
+        <v>113680425</v>
       </c>
       <c r="B179" t="n">
-        <v>103146</v>
+        <v>88985</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -19800,25 +19809,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>222412</v>
+        <v>1593</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19828,10 +19837,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>574350</v>
+        <v>574231</v>
       </c>
       <c r="R179" t="n">
-        <v>6703556</v>
+        <v>6703561</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19858,12 +19867,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19875,12 +19884,12 @@
       <c r="AG179" t="b">
         <v>0</v>
       </c>
-      <c r="AS179" t="inlineStr">
+      <c r="AT179" t="inlineStr"/>
+      <c r="AU179" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -19899,10 +19908,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>113680425</v>
+        <v>113680439</v>
       </c>
       <c r="B180" t="n">
-        <v>88985</v>
+        <v>91597</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19911,25 +19920,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1593</v>
+        <v>4361</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19939,10 +19948,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>574231</v>
+        <v>574162</v>
       </c>
       <c r="R180" t="n">
-        <v>6703561</v>
+        <v>6703584</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19969,12 +19978,12 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20010,10 +20019,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>113680439</v>
+        <v>113680443</v>
       </c>
       <c r="B181" t="n">
-        <v>91597</v>
+        <v>90105</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -20022,38 +20031,38 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>vreten, Gstr</t>
+          <t>Gropbacka, Gstr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>574162</v>
+        <v>574253</v>
       </c>
       <c r="R181" t="n">
-        <v>6703584</v>
+        <v>6703487</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20121,10 +20130,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>113680443</v>
+        <v>113680445</v>
       </c>
       <c r="B182" t="n">
-        <v>90105</v>
+        <v>91623</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -20133,38 +20142,38 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>3215</v>
+        <v>4368</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gropbacka, Gstr</t>
+          <t>Kalkberget, Gstr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>574253</v>
+        <v>574533</v>
       </c>
       <c r="R182" t="n">
-        <v>6703487</v>
+        <v>6703448</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20232,10 +20241,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>113680445</v>
+        <v>113680444</v>
       </c>
       <c r="B183" t="n">
-        <v>91623</v>
+        <v>90332</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -20248,34 +20257,34 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4368</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Kalkberget, Gstr</t>
+          <t>Gropbacka, Gstr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>574533</v>
+        <v>574448</v>
       </c>
       <c r="R183" t="n">
-        <v>6703448</v>
+        <v>6703387</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20343,10 +20352,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>113680444</v>
+        <v>113678027</v>
       </c>
       <c r="B184" t="n">
-        <v>90332</v>
+        <v>94059</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -20355,38 +20364,42 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Gropbacka, Gstr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>574448</v>
+        <v>574437</v>
       </c>
       <c r="R184" t="n">
-        <v>6703387</v>
+        <v>6703378</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20427,15 +20440,11 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
       <c r="AT184" t="inlineStr"/>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW184" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -20454,10 +20463,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>113678027</v>
+        <v>113678026</v>
       </c>
       <c r="B185" t="n">
-        <v>94059</v>
+        <v>95203</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -20466,25 +20475,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2809</v>
+        <v>53</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20494,14 +20503,14 @@
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Gropbacka, Gstr</t>
+          <t>vreten, Gstr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>574437</v>
+        <v>574254</v>
       </c>
       <c r="R185" t="n">
-        <v>6703378</v>
+        <v>6703549</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20565,10 +20574,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>113678026</v>
+        <v>113702571</v>
       </c>
       <c r="B186" t="n">
-        <v>95203</v>
+        <v>91626</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -20577,42 +20586,38 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>vreten, Gstr</t>
+          <t>Gropbacka, Gstr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>574254</v>
+        <v>574265</v>
       </c>
       <c r="R186" t="n">
-        <v>6703549</v>
+        <v>6703495</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20658,6 +20663,11 @@
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW186" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -20676,10 +20686,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>113702571</v>
+        <v>113678028</v>
       </c>
       <c r="B187" t="n">
-        <v>91626</v>
+        <v>94071</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -20692,34 +20702,38 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>5964</v>
+        <v>2813</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
           <t>Gropbacka, Gstr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>574265</v>
+        <v>574436</v>
       </c>
       <c r="R187" t="n">
-        <v>6703495</v>
+        <v>6703379</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20765,11 +20779,6 @@
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW187" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -20788,10 +20797,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>113678028</v>
+        <v>113702573</v>
       </c>
       <c r="B188" t="n">
-        <v>94071</v>
+        <v>91626</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -20804,38 +20813,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2813</v>
+        <v>5964</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Gropbacka, Gstr</t>
+          <t>vreten, Gstr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>574436</v>
+        <v>574313</v>
       </c>
       <c r="R188" t="n">
-        <v>6703379</v>
+        <v>6703557</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20881,6 +20886,11 @@
         <v>0</v>
       </c>
       <c r="AT188" t="inlineStr"/>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW188" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -20899,10 +20909,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>113702573</v>
+        <v>114567760</v>
       </c>
       <c r="B189" t="n">
-        <v>91626</v>
+        <v>99909</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -20915,34 +20925,38 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>vreten, Gstr</t>
+          <t>Horndal-Fallviken, Gstr</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>574313</v>
+        <v>574389</v>
       </c>
       <c r="R189" t="n">
-        <v>6703557</v>
+        <v>6703565</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20969,12 +20983,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-04-19</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20988,33 +21002,24 @@
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Mårten Nilsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Helene Andersson, Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>114567760</v>
+        <v>114567754</v>
       </c>
       <c r="B190" t="n">
-        <v>99909</v>
+        <v>97650</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -21023,25 +21028,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -21055,10 +21060,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>574389</v>
+        <v>574287</v>
       </c>
       <c r="R190" t="n">
-        <v>6703565</v>
+        <v>6703577</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21118,10 +21123,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>114567754</v>
+        <v>115904715</v>
       </c>
       <c r="B191" t="n">
-        <v>97650</v>
+        <v>79426</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -21130,42 +21135,38 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>388</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Horndal-Fallviken, Gstr</t>
+          <t>Kratte Masugn (Kratte Masugn), Gstr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>574287</v>
+        <v>574508</v>
       </c>
       <c r="R191" t="n">
-        <v>6703577</v>
+        <v>6703409</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21192,12 +21193,22 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>2024-04-12</t>
+        </is>
+      </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21206,29 +21217,28 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Mårten Nilsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>115904715</v>
+        <v>116467984</v>
       </c>
       <c r="B192" t="n">
-        <v>79426</v>
+        <v>79546</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -21237,41 +21247,41 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>388</v>
+        <v>6456</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Kratte Masugn (Kratte Masugn), Gstr</t>
+          <t>Kratte Masugn, Gstr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>574508</v>
+        <v>574507</v>
       </c>
       <c r="R192" t="n">
-        <v>6703409</v>
+        <v>6703478</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21295,22 +21305,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>17:31</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2024-04-12</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>17:31</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21330,17 +21330,17 @@
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Philipp Weiss, Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>116467984</v>
+        <v>116467986</v>
       </c>
       <c r="B193" t="n">
-        <v>79546</v>
+        <v>90442</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -21349,25 +21349,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21377,10 +21377,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>574507</v>
+        <v>574428</v>
       </c>
       <c r="R193" t="n">
-        <v>6703478</v>
+        <v>6703418</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>
@@ -21439,10 +21439,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>116467986</v>
+        <v>116467994</v>
       </c>
       <c r="B194" t="n">
-        <v>90442</v>
+        <v>90407</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -21451,25 +21451,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21479,10 +21479,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>574428</v>
+        <v>574318</v>
       </c>
       <c r="R194" t="n">
-        <v>6703418</v>
+        <v>6703542</v>
       </c>
       <c r="S194" t="n">
         <v>15</v>
@@ -21541,10 +21541,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>116467994</v>
+        <v>116467993</v>
       </c>
       <c r="B195" t="n">
-        <v>90407</v>
+        <v>90442</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -21553,25 +21553,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21581,10 +21581,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>574318</v>
+        <v>574341</v>
       </c>
       <c r="R195" t="n">
-        <v>6703542</v>
+        <v>6703552</v>
       </c>
       <c r="S195" t="n">
         <v>15</v>
@@ -21643,10 +21643,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>116467993</v>
+        <v>117451692</v>
       </c>
       <c r="B196" t="n">
-        <v>90442</v>
+        <v>96425</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -21655,41 +21655,41 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1202</v>
+        <v>1590</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Kratte Masugn, Gstr</t>
+          <t>Gästrikeleden (Gästrikeleden), Gstr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>574341</v>
+        <v>574279</v>
       </c>
       <c r="R196" t="n">
-        <v>6703552</v>
+        <v>6703591</v>
       </c>
       <c r="S196" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -21713,12 +21713,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21733,26 +21743,26 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Patric Engfeldt</t>
+          <t>Malte Lindberg</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>117451692</v>
+        <v>119738980</v>
       </c>
       <c r="B197" t="n">
-        <v>96425</v>
+        <v>94346</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -21761,37 +21771,37 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1590</v>
+        <v>2813</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Gästrikeleden (Gästrikeleden), Gstr</t>
+          <t>Kalkberget, Kalkberget, Gstr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>574279</v>
+        <v>574414</v>
       </c>
       <c r="R197" t="n">
-        <v>6703591</v>
+        <v>6703531</v>
       </c>
       <c r="S197" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -21815,22 +21825,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-06-01</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21845,22 +21855,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Urban Selander</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Malte Lindberg</t>
+          <t>Urban Selander</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119738980</v>
+        <v>119920840</v>
       </c>
       <c r="B198" t="n">
-        <v>94346</v>
+        <v>56271</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -21869,41 +21879,54 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>2813</v>
+        <v>205998</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Kalkberget, Kalkberget, Gstr</t>
+          <t>Karlfeltstugan, Gstr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>574414</v>
+        <v>574267</v>
       </c>
       <c r="R198" t="n">
-        <v>6703531</v>
+        <v>6703408</v>
       </c>
       <c r="S198" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -21927,22 +21950,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-09-14</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21957,78 +21980,65 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Urban Selander</t>
+          <t>Hanna Sohlborg</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Urban Selander</t>
+          <t>Hanna Sohlborg</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119920840</v>
+        <v>122753505</v>
       </c>
       <c r="B199" t="n">
-        <v>56271</v>
+        <v>100545</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>205998</v>
+        <v>222771</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N199" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Karlfeltstugan, Gstr</t>
+          <t>Fännsmyran S, Gstr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>574267</v>
+        <v>574278</v>
       </c>
       <c r="R199" t="n">
-        <v>6703408</v>
+        <v>6703471</v>
       </c>
       <c r="S199" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22052,22 +22062,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>15:44</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22082,22 +22082,26 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Hanna Sohlborg</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Hanna Sohlborg</t>
-        </is>
-      </c>
-      <c r="AY199" t="inlineStr"/>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122753505</v>
+        <v>122753502</v>
       </c>
       <c r="B200" t="n">
-        <v>100545</v>
+        <v>86490</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -22106,38 +22110,38 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>222771</v>
+        <v>3739</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Fännsmyran S, Gstr</t>
+          <t>Smedsrönningen SV, Gstr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>574278</v>
+        <v>574530</v>
       </c>
       <c r="R200" t="n">
-        <v>6703471</v>
+        <v>6703442</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22164,12 +22168,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22200,10 +22204,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122753502</v>
+        <v>122753507</v>
       </c>
       <c r="B201" t="n">
-        <v>86490</v>
+        <v>86431</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -22212,38 +22216,38 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>3739</v>
+        <v>3674</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Smedsrönningen SV, Gstr</t>
+          <t>Rismyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>574530</v>
+        <v>574322</v>
       </c>
       <c r="R201" t="n">
-        <v>6703442</v>
+        <v>6703415</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22270,12 +22274,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22306,10 +22310,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>122753507</v>
+        <v>122753503</v>
       </c>
       <c r="B202" t="n">
-        <v>86431</v>
+        <v>90494</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -22318,38 +22322,38 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Rismyran SV, Gstr</t>
+          <t>Slätahällsm. V, Gstr</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>574322</v>
+        <v>574232</v>
       </c>
       <c r="R202" t="n">
-        <v>6703415</v>
+        <v>6703559</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22412,10 +22416,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>122753503</v>
+        <v>122753508</v>
       </c>
       <c r="B203" t="n">
-        <v>90494</v>
+        <v>90504</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -22424,38 +22428,38 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5747</v>
+        <v>5754</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Slätahällsm. V, Gstr</t>
+          <t>Fännsmyran SV, Gstr</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>574232</v>
+        <v>574334</v>
       </c>
       <c r="R203" t="n">
-        <v>6703559</v>
+        <v>6703351</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22511,112 +22515,6 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>122753508</v>
-      </c>
-      <c r="B204" t="n">
-        <v>90504</v>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E204" t="n">
-        <v>5754</v>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Gultoppig fingersvamp</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Ramaria testaceoflava</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="P204" t="inlineStr">
-        <is>
-          <t>Fännsmyran SV, Gstr</t>
-        </is>
-      </c>
-      <c r="Q204" t="n">
-        <v>574334</v>
-      </c>
-      <c r="R204" t="n">
-        <v>6703351</v>
-      </c>
-      <c r="S204" t="n">
-        <v>10</v>
-      </c>
-      <c r="T204" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U204" t="inlineStr">
-        <is>
-          <t>Hofors</t>
-        </is>
-      </c>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr">
-        <is>
-          <t>Torsåker</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr">
-        <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>2023-09-19</t>
-        </is>
-      </c>
-      <c r="AD204" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE204" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG204" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT204" t="inlineStr"/>
-      <c r="AW204" t="inlineStr">
-        <is>
-          <t>Helene Andersson</t>
-        </is>
-      </c>
-      <c r="AX204" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY204" t="inlineStr">
         <is>
           <t xml:space="preserve">Naturvärdesinventering </t>
         </is>
